--- a/reports/pdf_rolling5_20261021.xlsx
+++ b/reports/pdf_rolling5_20261021.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,644억   ·   현금 141억(3.2%)      오늘 2026-10-21  vs  5일전 2026-10-14      매수 20종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,470억      오늘 2026-10-21  vs  5일전 2026-10-14      매수 20종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>291</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2964854574</v>
+        <v>2964855051</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-486</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-5468512861</v>
+        <v>-5468513741</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2350154811</v>
+        <v>2350155189</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-156</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2067003869</v>
+        <v>-2067004201</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>139</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>506378573</v>
+        <v>506378655</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-101</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1919533975</v>
+        <v>-1919534284</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>90</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2236500810</v>
+        <v>2236501170</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-95</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2535446418</v>
+        <v>-2535446826</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>725789243</v>
+        <v>821601070</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.83%→1.14%</t>
+          <t>0.90%→1.10%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>365→428</t>
+          <t>301→364</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>-73</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1690695212</v>
+        <v>-1690695484</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>821600938</v>
+        <v>725789360</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.10%</t>
+          <t>0.83%→1.14%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>301→364</t>
+          <t>365→428</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -906,7 +906,7 @@
         <v>-59</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2949894868</v>
+        <v>-2949895343</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>874720317</v>
+        <v>874720458</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-44</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-771940680</v>
+        <v>-771940804</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>37</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1296424970</v>
+        <v>1296425178</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-35</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-838439304</v>
+        <v>-838439439</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>33</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1407206310</v>
+        <v>1407206536</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-26</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1323213279</v>
+        <v>-1323213492</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1553821363</v>
+        <v>1553821613</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-25</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-936845339</v>
+        <v>-936845490</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스엠  (신규)</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1377386299</v>
+        <v>2640761181</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.55%</t>
+          <t>0.00%→0.61%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>23→54</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>-20</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-922432334</v>
+        <v>-922432483</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스엠  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2640760756</v>
+        <v>1377386521</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.61%</t>
+          <t>0.20%→0.55%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>23→54</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1561872766</v>
+        <v>-1561873017</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>29</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>457757046</v>
+        <v>457757119</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-17</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2646227758</v>
+        <v>-2646228184</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>26</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1098370398</v>
+        <v>1098370575</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-911895930</v>
+        <v>-911896077</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1298363270</v>
+        <v>1298363479</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1109304402</v>
+        <v>-1109304580</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>851858309</v>
+        <v>851858446</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1339,46 +1339,46 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-446007962</v>
+        <v>-816173827</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.26%</t>
+          <t>5.70%→4.66%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>826262799</v>
+        <v>1482551776</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.16%</t>
+          <t>1.44%→2.00%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>92→111</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1829954663</v>
+        <v>-1829954957</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1406,44 +1406,44 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1482551537</v>
+        <v>826262932</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.44%→2.00%</t>
+          <t>1.02%→1.16%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>92→111</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-743114669</v>
+        <v>-446008033</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.08%</t>
+          <t>0.32%→0.26%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1067158786</v>
+        <v>1067158958</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1471,23 +1471,23 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-816173696</v>
+        <v>-743114789</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>5.70%→4.66%</t>
+          <t>1.31%→1.08%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1586424575</v>
+        <v>1586424830</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1515,23 +1515,23 @@
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-950264344</v>
+        <v>-711704372</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.88%→0.77%</t>
+          <t>7.79%→7.40%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -1543,30 +1543,30 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-711704258</v>
+        <v>-950264497</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>7.79%→7.40%</t>
+          <t>0.88%→0.77%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,166억   ·   현금 59억(1.9%)      오늘 2026-10-21  vs  5일전 2026-10-14      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억      오늘 2026-10-21  vs  5일전 2026-10-14      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1662,7 +1662,7 @@
         <v>56</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1495871661</v>
+        <v>1501517364</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>-90</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-629639857</v>
+        <v>-632016238</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>51</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1000109774</v>
+        <v>1003884377</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>-20</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-2819599362</v>
+        <v>-2830241064</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>858838306</v>
+        <v>862079724</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>-19</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-928453790</v>
+        <v>-931957950</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>615965861</v>
+        <v>618290632</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>-17</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1778573597</v>
+        <v>-1785286271</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>620735859</v>
+        <v>623078634</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>-14</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2808469364</v>
+        <v>-2819069060</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>612149861</v>
+        <v>614460231</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>279627937</v>
+        <v>280683306</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,403억   ·   현금 40억(1.7%)      오늘 2026-10-21  vs  5일전 2026-10-14      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,290억      오늘 2026-10-21  vs  5일전 2026-10-14      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2027,7 +2027,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1769415215</v>
+        <v>1769415483</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>-50</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-802332597</v>
+        <v>-802332719</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>560018268</v>
+        <v>560018353</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>-25</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-716662587</v>
+        <v>-716662696</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>913835411</v>
+        <v>913835550</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>-14</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1213219147</v>
+        <v>-1213219331</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>-8</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-619987275</v>
+        <v>-619987369</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,071억   ·   현금 5억(0.3%)      오늘 2026-10-21  vs  5일전 2026-10-14      매수 2종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,073억      오늘 2026-10-21  vs  5일전 2026-10-14      매수 2종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2276,7 +2276,7 @@
         <v>108</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>8229209494</v>
+        <v>8357129385</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>-345</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-3116177354</v>
+        <v>-3164617130</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>26</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>13960073107</v>
+        <v>14177077063</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>-253</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-4057689059</v>
+        <v>-4120764272</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>-234</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-2059386773</v>
+        <v>-2091399147</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>-198</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1918342402</v>
+        <v>-1948162296</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>-148</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1259672139</v>
+        <v>-1279253257</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>-86</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-3239928929</v>
+        <v>-3290292375</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>-58</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-2064173172</v>
+        <v>-2096259949</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>-23</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-2050817575</v>
+        <v>-2082696744</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>-8</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1168807758</v>
+        <v>-1186976424</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 3억(1.1%)      오늘 2026-10-21  vs  5일전 2026-10-14      매수 8종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 269억      오늘 2026-10-21  vs  5일전 2026-10-14      매수 8종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2649,7 +2649,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>111983733</v>
+        <v>105853332</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2670,11 +2670,11 @@
         <v>-88</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-62320683</v>
+        <v>-56896417</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>7.99%→7.76%</t>
+          <t>7.65%→7.42%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2693,11 +2693,11 @@
         <v>34</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>32347581</v>
+        <v>29887369</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.30%→0.42%</t>
+          <t>0.29%→0.41%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2714,11 +2714,11 @@
         <v>-34</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-92828445</v>
+        <v>-86905726</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>8.28%→7.93%</t>
+          <t>8.12%→7.78%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2737,11 +2737,11 @@
         <v>24</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>55073967</v>
+        <v>52742416</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.50%</t>
+          <t>1.31%→1.50%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2758,11 +2758,11 @@
         <v>-31</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-54521217</v>
+        <v>-53171216</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>3.03%→2.83%</t>
+          <t>3.10%→2.89%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2781,11 +2781,11 @@
         <v>17</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>57291666</v>
+        <v>52849616</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.54%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2802,7 +2802,7 @@
         <v>-22</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-50926670</v>
+        <v>-47462814</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2825,11 +2825,11 @@
         <v>8</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>66088761</v>
+        <v>62872819</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.05%→2.28%</t>
+          <t>2.04%→2.27%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2846,11 +2846,11 @@
         <v>-19</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-30042782</v>
+        <v>-29024409</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>4.83%→4.71%</t>
+          <t>4.89%→4.77%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2869,11 +2869,11 @@
         <v>7</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>39395976</v>
+        <v>36816511</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.31%</t>
+          <t>1.15%→1.28%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2890,11 +2890,11 @@
         <v>-8</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-58959965</v>
+        <v>-54886416</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.25%→2.03%</t>
+          <t>2.19%→1.98%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2913,11 +2913,11 @@
         <v>6</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>64440562</v>
+        <v>62953219</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.50%</t>
+          <t>1.30%→1.54%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2934,11 +2934,11 @@
         <v>-6</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-50732370</v>
+        <v>-48802815</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.57%</t>
+          <t>2.78%→2.60%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2957,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>25165185</v>
+        <v>23597407</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>-3</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-8321395</v>
+        <v>-8160602</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20261021.xlsx
+++ b/reports/pdf_rolling5_20261021.xlsx
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>821601070</v>
+        <v>725789360</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.10%</t>
+          <t>0.83%→1.14%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>301→364</t>
+          <t>365→428</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>63</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>725789360</v>
+        <v>821601070</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.83%→1.14%</t>
+          <t>0.90%→1.10%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>365→428</t>
+          <t>301→364</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에스엠  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2640761181</v>
+        <v>1377386521</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.61%</t>
+          <t>0.20%→0.55%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>23→54</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스엠  (신규)</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1377386521</v>
+        <v>2640761181</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.55%</t>
+          <t>0.00%→0.61%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>23→54</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-816173827</v>
+        <v>-1829954957</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>5.70%→4.66%</t>
+          <t>2.91%→2.29%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1829954957</v>
+        <v>-743114789</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.91%→2.29%</t>
+          <t>1.31%→1.08%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1471,23 +1471,23 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-743114789</v>
+        <v>-816173827</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.08%</t>
+          <t>5.70%→4.66%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -2064,23 +2064,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>560018353</v>
+        <v>913835550</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.60%</t>
+          <t>7.28%→6.79%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>110→117</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2108,23 +2108,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>913835550</v>
+        <v>560018353</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>7.28%→6.79%</t>
+          <t>1.43%→1.60%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>110→117</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -2906,23 +2906,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>62953219</v>
+        <v>23597407</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.54%</t>
+          <t>0.12%→0.21%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>8→14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -2950,23 +2950,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>23597407</v>
+        <v>62953219</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.21%</t>
+          <t>1.30%→1.54%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>8→14</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261021.xlsx
+++ b/reports/pdf_rolling5_20261021.xlsx
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스엠  (신규)</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1377386521</v>
+        <v>2640761181</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.55%</t>
+          <t>0.00%→0.61%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>23→54</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스엠  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2640761181</v>
+        <v>1377386521</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.61%</t>
+          <t>0.20%→0.55%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>23→54</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1339,90 +1339,90 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1829954957</v>
+        <v>-743114789</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.91%→2.29%</t>
+          <t>1.31%→1.08%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1482551776</v>
+        <v>826262932</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.44%→2.00%</t>
+          <t>1.02%→1.16%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>92→111</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-743114789</v>
+        <v>-1829954957</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.08%</t>
+          <t>2.91%→2.29%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>826262932</v>
+        <v>1482551776</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.16%</t>
+          <t>1.44%→2.00%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>92→111</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -2064,23 +2064,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>913835550</v>
+        <v>560018353</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>7.28%→6.79%</t>
+          <t>1.43%→1.60%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>110→117</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2108,23 +2108,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>560018353</v>
+        <v>913835550</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.60%</t>
+          <t>7.28%→6.79%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>110→117</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
